--- a/sample_agreement_safexpress.xlsx
+++ b/sample_agreement_safexpress.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ZoneMatrix" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ZoneMapping" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Charges" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ZoneMatrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ZoneMapping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Charges" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Read Me" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1010,11 +1010,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Appointment Charge Amount (Rs, 0 = any positive value counts)</t>
+          <t>Appointment Charge Amount (Rs)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>750</v>
       </c>
     </row>
     <row r="10">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ahmedabad, Bengaluru, Chennai, Delhi, Hyderabad, Kolkata, Mumbai, Pune</t>
+          <t>Ahmedabad, Bengaluru, Bangalore, Chennai, Delhi, Hyderabad, Kolkata, Mumbai, Pune</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1067,19 +1067,33 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Charges: flat/percentage charge parameters used by the optional extra checks.</t>
+          <t>Charges: flat/percentage charge parameters used by the price calculation.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Replace the sample Safexpress figures with your own agreement, or use as-is.</t>
+          <t>Appointment Charge Amount: flat rupee amount added when Appointment based</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Delivery is selected for an AWB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Replace the sample Safexpress figures with your own agreement, or use as-is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Do not rename the sheet tabs (ZoneMatrix / ZoneMapping / Charges) or the tool cannot read them.</t>
         </is>
